--- a/docs/Amazon_FBA_vs_FBM_Projection.xlsx
+++ b/docs/Amazon_FBA_vs_FBM_Projection.xlsx
@@ -1,16 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Assumptions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Per-Unit" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Monthly" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Projection" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Per-Unit" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Projection" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Break-Even" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenarios" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -154,7 +156,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -202,6 +204,29 @@
     <xf numFmtId="166" fontId="7" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -279,14 +304,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -309,7 +334,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28000">
               <a:solidFill>
                 <a:srgbClr val="B26A16"/>
               </a:solidFill>
@@ -319,7 +344,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -344,7 +369,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28000">
               <a:solidFill>
                 <a:srgbClr val="1B2A4A"/>
               </a:solidFill>
@@ -354,7 +379,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -382,8 +407,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -409,8 +434,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -429,6 +454,257 @@
     <legend>
       <legendPos val="r"/>
     </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Net Profit vs Monthly Units</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Break-Even'!B4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28000">
+              <a:solidFill>
+                <a:srgbClr val="B26A16"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Break-Even'!$A$5:$A$20</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Break-Even'!$B$5:$B$20</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Break-Even'!C4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28000">
+              <a:solidFill>
+                <a:srgbClr val="1B2A4A"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Break-Even'!$A$5:$A$20</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Break-Even'!$C$5:$C$20</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Units / month</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Net profit $</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Monthly Net Profit by Scenario</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Scenarios'!F4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Scenarios'!$A$5:$A$8</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Scenarios'!$F$5:$F$8</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Net @ snapshot $</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
@@ -456,7 +732,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>9</col>
@@ -471,9 +747,63 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6120000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="3060000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2244,4 +2574,497 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Break-Even — Net Profit by Monthly Volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Net profit at each volume (capped at labor capacity). Where a line crosses $0 is that method's break-even.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="35" t="inlineStr">
+        <is>
+          <t>Units / month</t>
+        </is>
+      </c>
+      <c r="B4" s="36" t="inlineStr">
+        <is>
+          <t>FBA net</t>
+        </is>
+      </c>
+      <c r="C4" s="36" t="inlineStr">
+        <is>
+          <t>FBM net</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="B5" s="11">
+        <f>MIN(A5,Assumptions!$B$33)*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$22</f>
+        <v>-7840</v>
+      </c>
+      <c r="C5" s="11">
+        <f>MIN(A5,Assumptions!$B$32)*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$22</f>
+        <v>-7840</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="28" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" s="29">
+        <f>MIN(A6,Assumptions!$B$33)*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$22</f>
+        <v>-6790</v>
+      </c>
+      <c r="C6" s="29">
+        <f>MIN(A6,Assumptions!$B$32)*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$22</f>
+        <v>-6890</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="n">
+        <v>200</v>
+      </c>
+      <c r="B7" s="11">
+        <f>MIN(A7,Assumptions!$B$33)*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$22</f>
+        <v>-5740</v>
+      </c>
+      <c r="C7" s="11">
+        <f>MIN(A7,Assumptions!$B$32)*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$22</f>
+        <v>-5940</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="28" t="n">
+        <v>300</v>
+      </c>
+      <c r="B8" s="29">
+        <f>MIN(A8,Assumptions!$B$33)*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$22</f>
+        <v>-4690</v>
+      </c>
+      <c r="C8" s="29">
+        <f>MIN(A8,Assumptions!$B$32)*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$22</f>
+        <v>-4990</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="n">
+        <v>400</v>
+      </c>
+      <c r="B9" s="11">
+        <f>MIN(A9,Assumptions!$B$33)*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$22</f>
+        <v>-3640</v>
+      </c>
+      <c r="C9" s="11">
+        <f>MIN(A9,Assumptions!$B$32)*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$22</f>
+        <v>-4040</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="28" t="n">
+        <v>500</v>
+      </c>
+      <c r="B10" s="29">
+        <f>MIN(A10,Assumptions!$B$33)*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$22</f>
+        <v>-2590</v>
+      </c>
+      <c r="C10" s="29">
+        <f>MIN(A10,Assumptions!$B$32)*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$22</f>
+        <v>-3090</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="n">
+        <v>600</v>
+      </c>
+      <c r="B11" s="11">
+        <f>MIN(A11,Assumptions!$B$33)*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$22</f>
+        <v>-1540</v>
+      </c>
+      <c r="C11" s="11">
+        <f>MIN(A11,Assumptions!$B$32)*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$22</f>
+        <v>-2140</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="28" t="n">
+        <v>700</v>
+      </c>
+      <c r="B12" s="29">
+        <f>MIN(A12,Assumptions!$B$33)*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$22</f>
+        <v>-490</v>
+      </c>
+      <c r="C12" s="29">
+        <f>MIN(A12,Assumptions!$B$32)*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$22</f>
+        <v>-1190</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="n">
+        <v>800</v>
+      </c>
+      <c r="B13" s="11">
+        <f>MIN(A13,Assumptions!$B$33)*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$22</f>
+        <v>560</v>
+      </c>
+      <c r="C13" s="11">
+        <f>MIN(A13,Assumptions!$B$32)*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$22</f>
+        <v>-240</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="28" t="n">
+        <v>900</v>
+      </c>
+      <c r="B14" s="29">
+        <f>MIN(A14,Assumptions!$B$33)*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$22</f>
+        <v>1610</v>
+      </c>
+      <c r="C14" s="29">
+        <f>MIN(A14,Assumptions!$B$32)*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$22</f>
+        <v>710</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="B15" s="11">
+        <f>MIN(A15,Assumptions!$B$33)*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$22</f>
+        <v>2660</v>
+      </c>
+      <c r="C15" s="11">
+        <f>MIN(A15,Assumptions!$B$32)*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$22</f>
+        <v>1660</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="28" t="n">
+        <v>1100</v>
+      </c>
+      <c r="B16" s="29">
+        <f>MIN(A16,Assumptions!$B$33)*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$22</f>
+        <v>3710</v>
+      </c>
+      <c r="C16" s="29">
+        <f>MIN(A16,Assumptions!$B$32)*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$22</f>
+        <v>2135</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="n">
+        <v>1200</v>
+      </c>
+      <c r="B17" s="11">
+        <f>MIN(A17,Assumptions!$B$33)*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$22</f>
+        <v>4760</v>
+      </c>
+      <c r="C17" s="11">
+        <f>MIN(A17,Assumptions!$B$32)*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$22</f>
+        <v>2135</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="28" t="n">
+        <v>1300</v>
+      </c>
+      <c r="B18" s="29">
+        <f>MIN(A18,Assumptions!$B$33)*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$22</f>
+        <v>5810</v>
+      </c>
+      <c r="C18" s="29">
+        <f>MIN(A18,Assumptions!$B$32)*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$22</f>
+        <v>2135</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="n">
+        <v>1400</v>
+      </c>
+      <c r="B19" s="11">
+        <f>MIN(A19,Assumptions!$B$33)*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$22</f>
+        <v>6860</v>
+      </c>
+      <c r="C19" s="11">
+        <f>MIN(A19,Assumptions!$B$32)*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$22</f>
+        <v>2135</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="28" t="n">
+        <v>1500</v>
+      </c>
+      <c r="B20" s="29">
+        <f>MIN(A20,Assumptions!$B$33)*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$22</f>
+        <v>7910</v>
+      </c>
+      <c r="C20" s="29">
+        <f>MIN(A20,Assumptions!$B$32)*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$22</f>
+        <v>2135</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t>Break-even units</t>
+        </is>
+      </c>
+      <c r="B22" s="37">
+        <f>(Assumptions!$B$13+Assumptions!$B$22)/'Per-Unit'!$B$12</f>
+        <v>746.6666666666666</v>
+      </c>
+      <c r="C22" s="37">
+        <f>(Assumptions!$B$13+Assumptions!$B$22)/'Per-Unit'!$C$12</f>
+        <v>825.2631578947369</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Break-even = fixed costs (plan + labor) ÷ contribution per unit</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A23:C23"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Scenario Comparison — Referral × Fulfillment</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Contribution, break-even and monthly net at the snapshot volume. Referral column is editable (blue).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="25" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B4" s="25" t="inlineStr">
+        <is>
+          <t>Referral</t>
+        </is>
+      </c>
+      <c r="C4" s="25" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="D4" s="25" t="inlineStr">
+        <is>
+          <t>Contribution/unit</t>
+        </is>
+      </c>
+      <c r="E4" s="25" t="inlineStr">
+        <is>
+          <t>Break-even units</t>
+        </is>
+      </c>
+      <c r="F4" s="25" t="inlineStr">
+        <is>
+          <t>Net @ snapshot</t>
+        </is>
+      </c>
+      <c r="G4" s="25" t="inlineStr">
+        <is>
+          <t>Net margin %</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="38" t="inlineStr">
+        <is>
+          <t>Low fee · FBM</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C5" s="39" t="inlineStr">
+        <is>
+          <t>FBM</t>
+        </is>
+      </c>
+      <c r="D5" s="40">
+        <f>Assumptions!$B$5-Assumptions!$B$6-Assumptions!$B$5*B5-Assumptions!$B$16</f>
+        <v>11.600000000000001</v>
+      </c>
+      <c r="E5" s="41">
+        <f>(Assumptions!$B$13+Assumptions!$B$22)/D5</f>
+        <v>675.8620689655172</v>
+      </c>
+      <c r="F5" s="42">
+        <f>MIN(Assumptions!$B$25,Assumptions!$B$32)*D5-Assumptions!$B$13-Assumptions!$B$22</f>
+        <v>2600.000000000002</v>
+      </c>
+      <c r="G5" s="43">
+        <f>F5/(MIN(Assumptions!$B$25,Assumptions!$B$32)*Assumptions!$B$5)</f>
+        <v>0.09629629629629637</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="44" t="inlineStr">
+        <is>
+          <t>Low fee · FBA</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C6" s="45" t="inlineStr">
+        <is>
+          <t>FBA</t>
+        </is>
+      </c>
+      <c r="D6" s="46">
+        <f>Assumptions!$B$5-Assumptions!$B$6-Assumptions!$B$5*B6-Assumptions!$B$11-Assumptions!$B$12</f>
+        <v>12.600000000000001</v>
+      </c>
+      <c r="E6" s="47">
+        <f>(Assumptions!$B$13+Assumptions!$B$22)/D6</f>
+        <v>622.2222222222222</v>
+      </c>
+      <c r="F6" s="48">
+        <f>MIN(Assumptions!$B$25,Assumptions!$B$33)*D6-Assumptions!$B$13-Assumptions!$B$22</f>
+        <v>3500.000000000002</v>
+      </c>
+      <c r="G6" s="49">
+        <f>F6/(MIN(Assumptions!$B$25,Assumptions!$B$33)*Assumptions!$B$5)</f>
+        <v>0.1296296296296297</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="38" t="inlineStr">
+        <is>
+          <t>Typical · FBM</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C7" s="39" t="inlineStr">
+        <is>
+          <t>FBM</t>
+        </is>
+      </c>
+      <c r="D7" s="40">
+        <f>Assumptions!$B$5-Assumptions!$B$6-Assumptions!$B$5*B7-Assumptions!$B$16</f>
+        <v>9.5</v>
+      </c>
+      <c r="E7" s="41">
+        <f>(Assumptions!$B$13+Assumptions!$B$22)/D7</f>
+        <v>825.2631578947369</v>
+      </c>
+      <c r="F7" s="42">
+        <f>MIN(Assumptions!$B$25,Assumptions!$B$32)*D7-Assumptions!$B$13-Assumptions!$B$22</f>
+        <v>710</v>
+      </c>
+      <c r="G7" s="43">
+        <f>F7/(MIN(Assumptions!$B$25,Assumptions!$B$32)*Assumptions!$B$5)</f>
+        <v>0.026296296296296297</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="44" t="inlineStr">
+        <is>
+          <t>Typical · FBA</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C8" s="45" t="inlineStr">
+        <is>
+          <t>FBA</t>
+        </is>
+      </c>
+      <c r="D8" s="46">
+        <f>Assumptions!$B$5-Assumptions!$B$6-Assumptions!$B$5*B8-Assumptions!$B$11-Assumptions!$B$12</f>
+        <v>10.5</v>
+      </c>
+      <c r="E8" s="47">
+        <f>(Assumptions!$B$13+Assumptions!$B$22)/D8</f>
+        <v>746.6666666666666</v>
+      </c>
+      <c r="F8" s="48">
+        <f>MIN(Assumptions!$B$25,Assumptions!$B$33)*D8-Assumptions!$B$13-Assumptions!$B$22</f>
+        <v>1610</v>
+      </c>
+      <c r="G8" s="49">
+        <f>F8/(MIN(Assumptions!$B$25,Assumptions!$B$33)*Assumptions!$B$5)</f>
+        <v>0.05962962962962963</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Net @ snapshot uses Assumptions!B25 units, capped at each method's capacity.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A10:G10"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>
--- a/docs/Amazon_FBA_vs_FBM_Projection.xlsx
+++ b/docs/Amazon_FBA_vs_FBM_Projection.xlsx
@@ -722,9 +722,9 @@
         <t>2026 FBA fulfillment ~$3-5 for small/standard items. Source: amzprep.com/amazon-fba-fees.</t>
       </text>
     </comment>
-    <comment ref="B12" authorId="0" shapeId="0">
+    <comment ref="B22" authorId="0" shapeId="0">
       <text>
-        <t>Storage ~$0.87/ft3 (Jan-Sep), ~$2.40 Q4; aged surcharge after 180 days. Enter a per-item average.</t>
+        <t>Your point: with FBA you only use employees you already have at the store, so the incremental payroll is $0.</t>
       </text>
     </comment>
   </commentList>
@@ -1101,12 +1101,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="54" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1119,7 +1119,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>FBA vs FBM comparison · 3 employees · 66.6% gross margin</t>
+          <t>FBA vs FBM · 3 employees · 66.6% gross margin · FBA uses existing store staff</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>LABOR</t>
+          <t>LABOR  (key difference between the two)</t>
         </is>
       </c>
       <c r="B18" s="4" t="n"/>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Given.</t>
+          <t>Existing store staff.</t>
         </is>
       </c>
     </row>
@@ -1313,170 +1313,219 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Share of staff time on Amazon</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="n">
-        <v>1</v>
+          <t>Store payroll (reference)</t>
+        </is>
+      </c>
+      <c r="B21" s="11">
+        <f>B19*B20</f>
+        <v>7800</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>100% = fully dedicated. Lower if staff also run the shop.</t>
+          <t>Employees × wage. Already paid for the shop.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Total monthly labor (Amazon)</t>
-        </is>
-      </c>
-      <c r="B22" s="11">
-        <f>B19*B20*B21</f>
-        <v>7800</v>
+          <t>FBA labor charged to Amazon (% payroll)</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Employees × wage × share.</t>
+          <t>0% = existing staff list in spare time; no new payroll.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>FBM labor charged to Amazon (% payroll)</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Packing &amp; shipping is real added work — a dedicated crew.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>VOLUME</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="n"/>
-      <c r="C24" s="4" t="n"/>
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>FBA monthly labor</t>
+        </is>
+      </c>
+      <c r="B24" s="11">
+        <f>B21*B22</f>
+        <v>0</v>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Payroll × FBA share.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
+          <t>FBM monthly labor</t>
+        </is>
+      </c>
+      <c r="B25" s="11">
+        <f>B21*B23</f>
+        <v>7800</v>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Payroll × FBM share.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>VOLUME</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n"/>
+      <c r="C27" s="4" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
           <t>Units / month — snapshot</t>
         </is>
       </c>
-      <c r="B25" s="10" t="n">
+      <c r="B28" s="10" t="n">
         <v>900</v>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>Volume used on the 'Monthly' sheet.</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>Month-1 units (projection)</t>
         </is>
       </c>
-      <c r="B26" s="10" t="n">
+      <c r="B29" s="10" t="n">
         <v>700</v>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>Starting volume for the 12-month projection.</t>
         </is>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>Monthly growth rate</t>
-        </is>
-      </c>
-      <c r="B27" s="8" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Unit growth applied each month.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>LABOR CAPACITY (units / employee / month)</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="n"/>
-      <c r="C29" s="4" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>FBM capacity / employee</t>
-        </is>
-      </c>
-      <c r="B30" s="10" t="n">
-        <v>350</v>
+          <t>Monthly growth rate</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="n">
+        <v>0.06</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Fewer — staff pack &amp; ship every order.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>FBA capacity / employee</t>
-        </is>
-      </c>
-      <c r="B31" s="10" t="n">
-        <v>700</v>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>More — Amazon fulfills; staff source &amp; list.</t>
+          <t>Unit growth applied each month.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>FBM total capacity</t>
-        </is>
-      </c>
-      <c r="B32" s="12">
-        <f>B19*B30*B21</f>
-        <v>1050</v>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Employees × FBM capacity × share.</t>
-        </is>
-      </c>
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>LABOR CAPACITY (units / employee / month)</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="n"/>
+      <c r="C32" s="4" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
+          <t>FBM capacity / employee</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="n">
+        <v>350</v>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Fewer — staff pack &amp; ship every order.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>FBA capacity / employee</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="n">
+        <v>700</v>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>More — Amazon fulfills; staff source &amp; list only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>FBM total capacity</t>
+        </is>
+      </c>
+      <c r="B35" s="12">
+        <f>B19*B33</f>
+        <v>1050</v>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Employees × FBM capacity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
           <t>FBA total capacity</t>
         </is>
       </c>
-      <c r="B33" s="12">
-        <f>B19*B31*B21</f>
+      <c r="B36" s="12">
+        <f>B19*B34</f>
         <v>2100</v>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Employees × FBA capacity × share.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="13" t="inlineStr">
-        <is>
-          <t>Blue = editable input (yellow fill). Black = formula. Fee/storage are 2026 planning estimates from public sources — confirm in Seller Central. Wages &amp; capacity are assumptions; adjust to ABC's reality.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Employees × FBA capacity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="13" t="inlineStr">
+        <is>
+          <t>Blue = editable input (yellow). Black = formula. KEY: FBA labor defaults to 0% — with FBA, Amazon fulfills, so existing store staff run it in spare time and ABC adds no payroll. FBM defaults to 100% because packing &amp; shipping ties up a dedicated crew. If existing staff also cover FBM in spare time, lower B23 — but then the FBM capacity limit (B35) bites sooner. Fee/storage are 2026 estimates; confirm in Seller Central.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A35:C36"/>
+    <mergeCell ref="A38:C41"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -1507,7 +1556,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>One average item, before monthly overhead (plan + labor)</t>
+          <t>One average item, before monthly overhead (plan + any labor)</t>
         </is>
       </c>
     </row>
@@ -1678,7 +1727,7 @@
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>Contribution/unit = what one sale adds before the $40 plan and wages. FBM has no FBA fee/storage but carries your own shipping — and ties up more staff time per order (see capacity).</t>
+          <t>Contribution/unit = what one sale adds before the $40 plan and any labor. Labor differs by method and lives on the Monthly/Projection sheets, not here.</t>
         </is>
       </c>
     </row>
@@ -1698,7 +1747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1716,7 +1765,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>At the snapshot volume (Assumptions!B25), capped at each method's labor capacity</t>
+          <t>Snapshot volume (Assumptions!B28), capped at capacity. FBA adds no payroll; FBM carries a dedicated crew.</t>
         </is>
       </c>
     </row>
@@ -1744,11 +1793,11 @@
         </is>
       </c>
       <c r="B4" s="12">
-        <f>MIN(Assumptions!$B$25,Assumptions!$B$33)</f>
+        <f>MIN(Assumptions!$B$28,Assumptions!$B$36)</f>
         <v>900</v>
       </c>
       <c r="C4" s="12">
-        <f>MIN(Assumptions!$B$25,Assumptions!$B$32)</f>
+        <f>MIN(Assumptions!$B$28,Assumptions!$B$35)</f>
         <v>900</v>
       </c>
     </row>
@@ -1872,15 +1921,15 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Labor (Amazon share)</t>
+          <t>Labor charged to Amazon</t>
         </is>
       </c>
       <c r="B13" s="11">
-        <f>-Assumptions!$B$22</f>
-        <v>-7800</v>
+        <f>-Assumptions!$B$24</f>
+        <v>0</v>
       </c>
       <c r="C13" s="11">
-        <f>-Assumptions!$B$22</f>
+        <f>-Assumptions!$B$25</f>
         <v>-7800</v>
       </c>
     </row>
@@ -1892,7 +1941,7 @@
       </c>
       <c r="B14" s="22">
         <f>B7+B8+B9+B10+B11+B12+B13</f>
-        <v>1610</v>
+        <v>9410</v>
       </c>
       <c r="C14" s="22">
         <f>C7+C8+C9+C10+C11+C12+C13</f>
@@ -1907,7 +1956,7 @@
       </c>
       <c r="B15" s="20">
         <f>B14/B5</f>
-        <v>0.05962962962962963</v>
+        <v>0.3485185185185185</v>
       </c>
       <c r="C15" s="20">
         <f>C14/C5</f>
@@ -1943,11 +1992,11 @@
         </is>
       </c>
       <c r="B19" s="11">
-        <f>Assumptions!$B$13+Assumptions!$B$22</f>
-        <v>7840</v>
+        <f>Assumptions!$B$13+Assumptions!$B$24</f>
+        <v>40</v>
       </c>
       <c r="C19" s="11">
-        <f>Assumptions!$B$13+Assumptions!$B$22</f>
+        <f>Assumptions!$B$13+Assumptions!$B$25</f>
         <v>7840</v>
       </c>
     </row>
@@ -1959,7 +2008,7 @@
       </c>
       <c r="B20" s="12">
         <f>B19/B18</f>
-        <v>746.6666666666666</v>
+        <v>3.8095238095238093</v>
       </c>
       <c r="C20" s="12">
         <f>C19/C18</f>
@@ -1973,11 +2022,11 @@
         </is>
       </c>
       <c r="B21" s="12">
-        <f>Assumptions!$B$33</f>
+        <f>Assumptions!$B$36</f>
         <v>2100</v>
       </c>
       <c r="C21" s="12">
-        <f>Assumptions!$B$32</f>
+        <f>Assumptions!$B$35</f>
         <v>1050</v>
       </c>
     </row>
@@ -2015,23 +2064,24 @@
       </c>
       <c r="B25" s="24">
         <f>B14-C14</f>
-        <v>900</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
         <is>
-          <t>Same wage bill both ways, but FBM staff process fewer orders each (they pack &amp; ship), so FBM caps out sooner as volume grows. FBM avoids FBA fees + storage risk on unsold one-off pawn items; FBA scales further on the same headcount. Change the blue inputs to test ABC's real numbers.</t>
+          <t>Big driver: FBA labor = $0 by default (existing store staff, no new payroll), while FBM carries a dedicated crew (Assumptions B23). That's why FBA looks far stronger. FBM still hits a labor-capacity ceiling as volume grows. Change the blue inputs — especially B22/B23 — to match ABC's real staffing.</t>
         </is>
       </c>
     </row>
     <row r="28"/>
     <row r="29"/>
     <row r="30"/>
+    <row r="31"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B24:C24"/>
-    <mergeCell ref="A27:C30"/>
+    <mergeCell ref="A27:C31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2066,7 +2116,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Demand grows from Month-1 units at the growth rate; each method is capped at its labor capacity.</t>
+          <t>Demand grows from Month-1 units; each method capped at its labor capacity. FBA carries no new payroll.</t>
         </is>
       </c>
     </row>
@@ -2117,27 +2167,27 @@
         <v>1</v>
       </c>
       <c r="B5" s="12">
-        <f>Assumptions!$B$26</f>
+        <f>Assumptions!$B$29</f>
         <v>700</v>
       </c>
       <c r="C5" s="12">
-        <f>MIN(B5,Assumptions!$B$33)</f>
+        <f>MIN(B5,Assumptions!$B$36)</f>
         <v>700</v>
       </c>
       <c r="D5" s="11">
-        <f>C5*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$22</f>
-        <v>-490</v>
+        <f>C5*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$24</f>
+        <v>7310</v>
       </c>
       <c r="E5" s="11">
         <f>D5</f>
-        <v>-490</v>
+        <v>7310</v>
       </c>
       <c r="F5" s="12">
-        <f>MIN(B5,Assumptions!$B$32)</f>
+        <f>MIN(B5,Assumptions!$B$35)</f>
         <v>700</v>
       </c>
       <c r="G5" s="11">
-        <f>F5*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$22</f>
+        <f>F5*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$25</f>
         <v>-1190</v>
       </c>
       <c r="H5" s="11">
@@ -2150,27 +2200,27 @@
         <v>2</v>
       </c>
       <c r="B6" s="28">
-        <f>ROUND(B5*(1+Assumptions!$B$27),0)</f>
+        <f>ROUND(B5*(1+Assumptions!$B$30),0)</f>
         <v>742</v>
       </c>
       <c r="C6" s="28">
-        <f>MIN(B6,Assumptions!$B$33)</f>
+        <f>MIN(B6,Assumptions!$B$36)</f>
         <v>742</v>
       </c>
       <c r="D6" s="29">
-        <f>C6*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$22</f>
-        <v>-49</v>
+        <f>C6*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$24</f>
+        <v>7751</v>
       </c>
       <c r="E6" s="29">
         <f>E5+D6</f>
-        <v>-539</v>
+        <v>15061</v>
       </c>
       <c r="F6" s="28">
-        <f>MIN(B6,Assumptions!$B$32)</f>
+        <f>MIN(B6,Assumptions!$B$35)</f>
         <v>742</v>
       </c>
       <c r="G6" s="29">
-        <f>F6*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$22</f>
+        <f>F6*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$25</f>
         <v>-791</v>
       </c>
       <c r="H6" s="29">
@@ -2183,27 +2233,27 @@
         <v>3</v>
       </c>
       <c r="B7" s="12">
-        <f>ROUND(B6*(1+Assumptions!$B$27),0)</f>
+        <f>ROUND(B6*(1+Assumptions!$B$30),0)</f>
         <v>787</v>
       </c>
       <c r="C7" s="12">
-        <f>MIN(B7,Assumptions!$B$33)</f>
+        <f>MIN(B7,Assumptions!$B$36)</f>
         <v>787</v>
       </c>
       <c r="D7" s="11">
-        <f>C7*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$22</f>
-        <v>423.5</v>
+        <f>C7*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$24</f>
+        <v>8223.5</v>
       </c>
       <c r="E7" s="11">
         <f>E6+D7</f>
-        <v>-115.5</v>
+        <v>23284.5</v>
       </c>
       <c r="F7" s="12">
-        <f>MIN(B7,Assumptions!$B$32)</f>
+        <f>MIN(B7,Assumptions!$B$35)</f>
         <v>787</v>
       </c>
       <c r="G7" s="11">
-        <f>F7*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$22</f>
+        <f>F7*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$25</f>
         <v>-363.5</v>
       </c>
       <c r="H7" s="11">
@@ -2216,27 +2266,27 @@
         <v>4</v>
       </c>
       <c r="B8" s="28">
-        <f>ROUND(B7*(1+Assumptions!$B$27),0)</f>
+        <f>ROUND(B7*(1+Assumptions!$B$30),0)</f>
         <v>834</v>
       </c>
       <c r="C8" s="28">
-        <f>MIN(B8,Assumptions!$B$33)</f>
+        <f>MIN(B8,Assumptions!$B$36)</f>
         <v>834</v>
       </c>
       <c r="D8" s="29">
-        <f>C8*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$22</f>
-        <v>917</v>
+        <f>C8*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$24</f>
+        <v>8717</v>
       </c>
       <c r="E8" s="29">
         <f>E7+D8</f>
-        <v>801.5</v>
+        <v>32001.5</v>
       </c>
       <c r="F8" s="28">
-        <f>MIN(B8,Assumptions!$B$32)</f>
+        <f>MIN(B8,Assumptions!$B$35)</f>
         <v>834</v>
       </c>
       <c r="G8" s="29">
-        <f>F8*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$22</f>
+        <f>F8*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$25</f>
         <v>83</v>
       </c>
       <c r="H8" s="29">
@@ -2249,27 +2299,27 @@
         <v>5</v>
       </c>
       <c r="B9" s="12">
-        <f>ROUND(B8*(1+Assumptions!$B$27),0)</f>
+        <f>ROUND(B8*(1+Assumptions!$B$30),0)</f>
         <v>884</v>
       </c>
       <c r="C9" s="12">
-        <f>MIN(B9,Assumptions!$B$33)</f>
+        <f>MIN(B9,Assumptions!$B$36)</f>
         <v>884</v>
       </c>
       <c r="D9" s="11">
-        <f>C9*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$22</f>
-        <v>1442</v>
+        <f>C9*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$24</f>
+        <v>9242</v>
       </c>
       <c r="E9" s="11">
         <f>E8+D9</f>
-        <v>2243.5</v>
+        <v>41243.5</v>
       </c>
       <c r="F9" s="12">
-        <f>MIN(B9,Assumptions!$B$32)</f>
+        <f>MIN(B9,Assumptions!$B$35)</f>
         <v>884</v>
       </c>
       <c r="G9" s="11">
-        <f>F9*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$22</f>
+        <f>F9*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$25</f>
         <v>558</v>
       </c>
       <c r="H9" s="11">
@@ -2282,27 +2332,27 @@
         <v>6</v>
       </c>
       <c r="B10" s="28">
-        <f>ROUND(B9*(1+Assumptions!$B$27),0)</f>
+        <f>ROUND(B9*(1+Assumptions!$B$30),0)</f>
         <v>937</v>
       </c>
       <c r="C10" s="28">
-        <f>MIN(B10,Assumptions!$B$33)</f>
+        <f>MIN(B10,Assumptions!$B$36)</f>
         <v>937</v>
       </c>
       <c r="D10" s="29">
-        <f>C10*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$22</f>
-        <v>1998.5</v>
+        <f>C10*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$24</f>
+        <v>9798.5</v>
       </c>
       <c r="E10" s="29">
         <f>E9+D10</f>
-        <v>4242</v>
+        <v>51042</v>
       </c>
       <c r="F10" s="28">
-        <f>MIN(B10,Assumptions!$B$32)</f>
+        <f>MIN(B10,Assumptions!$B$35)</f>
         <v>937</v>
       </c>
       <c r="G10" s="29">
-        <f>F10*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$22</f>
+        <f>F10*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$25</f>
         <v>1061.5</v>
       </c>
       <c r="H10" s="29">
@@ -2315,27 +2365,27 @@
         <v>7</v>
       </c>
       <c r="B11" s="12">
-        <f>ROUND(B10*(1+Assumptions!$B$27),0)</f>
+        <f>ROUND(B10*(1+Assumptions!$B$30),0)</f>
         <v>993</v>
       </c>
       <c r="C11" s="12">
-        <f>MIN(B11,Assumptions!$B$33)</f>
+        <f>MIN(B11,Assumptions!$B$36)</f>
         <v>993</v>
       </c>
       <c r="D11" s="11">
-        <f>C11*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$22</f>
-        <v>2586.5</v>
+        <f>C11*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$24</f>
+        <v>10386.5</v>
       </c>
       <c r="E11" s="11">
         <f>E10+D11</f>
-        <v>6828.5</v>
+        <v>61428.5</v>
       </c>
       <c r="F11" s="12">
-        <f>MIN(B11,Assumptions!$B$32)</f>
+        <f>MIN(B11,Assumptions!$B$35)</f>
         <v>993</v>
       </c>
       <c r="G11" s="11">
-        <f>F11*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$22</f>
+        <f>F11*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$25</f>
         <v>1593.5</v>
       </c>
       <c r="H11" s="11">
@@ -2348,27 +2398,27 @@
         <v>8</v>
       </c>
       <c r="B12" s="28">
-        <f>ROUND(B11*(1+Assumptions!$B$27),0)</f>
+        <f>ROUND(B11*(1+Assumptions!$B$30),0)</f>
         <v>1053</v>
       </c>
       <c r="C12" s="28">
-        <f>MIN(B12,Assumptions!$B$33)</f>
+        <f>MIN(B12,Assumptions!$B$36)</f>
         <v>1053</v>
       </c>
       <c r="D12" s="29">
-        <f>C12*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$22</f>
-        <v>3216.5</v>
+        <f>C12*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$24</f>
+        <v>11016.5</v>
       </c>
       <c r="E12" s="29">
         <f>E11+D12</f>
-        <v>10045</v>
+        <v>72445</v>
       </c>
       <c r="F12" s="28">
-        <f>MIN(B12,Assumptions!$B$32)</f>
+        <f>MIN(B12,Assumptions!$B$35)</f>
         <v>1050</v>
       </c>
       <c r="G12" s="29">
-        <f>F12*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$22</f>
+        <f>F12*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$25</f>
         <v>2135</v>
       </c>
       <c r="H12" s="29">
@@ -2381,27 +2431,27 @@
         <v>9</v>
       </c>
       <c r="B13" s="12">
-        <f>ROUND(B12*(1+Assumptions!$B$27),0)</f>
+        <f>ROUND(B12*(1+Assumptions!$B$30),0)</f>
         <v>1116</v>
       </c>
       <c r="C13" s="12">
-        <f>MIN(B13,Assumptions!$B$33)</f>
+        <f>MIN(B13,Assumptions!$B$36)</f>
         <v>1116</v>
       </c>
       <c r="D13" s="11">
-        <f>C13*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$22</f>
-        <v>3878</v>
+        <f>C13*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$24</f>
+        <v>11678</v>
       </c>
       <c r="E13" s="11">
         <f>E12+D13</f>
-        <v>13923</v>
+        <v>84123</v>
       </c>
       <c r="F13" s="12">
-        <f>MIN(B13,Assumptions!$B$32)</f>
+        <f>MIN(B13,Assumptions!$B$35)</f>
         <v>1050</v>
       </c>
       <c r="G13" s="11">
-        <f>F13*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$22</f>
+        <f>F13*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$25</f>
         <v>2135</v>
       </c>
       <c r="H13" s="11">
@@ -2414,27 +2464,27 @@
         <v>10</v>
       </c>
       <c r="B14" s="28">
-        <f>ROUND(B13*(1+Assumptions!$B$27),0)</f>
+        <f>ROUND(B13*(1+Assumptions!$B$30),0)</f>
         <v>1183</v>
       </c>
       <c r="C14" s="28">
-        <f>MIN(B14,Assumptions!$B$33)</f>
+        <f>MIN(B14,Assumptions!$B$36)</f>
         <v>1183</v>
       </c>
       <c r="D14" s="29">
-        <f>C14*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$22</f>
-        <v>4581.5</v>
+        <f>C14*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$24</f>
+        <v>12381.5</v>
       </c>
       <c r="E14" s="29">
         <f>E13+D14</f>
-        <v>18504.5</v>
+        <v>96504.5</v>
       </c>
       <c r="F14" s="28">
-        <f>MIN(B14,Assumptions!$B$32)</f>
+        <f>MIN(B14,Assumptions!$B$35)</f>
         <v>1050</v>
       </c>
       <c r="G14" s="29">
-        <f>F14*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$22</f>
+        <f>F14*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$25</f>
         <v>2135</v>
       </c>
       <c r="H14" s="29">
@@ -2447,27 +2497,27 @@
         <v>11</v>
       </c>
       <c r="B15" s="12">
-        <f>ROUND(B14*(1+Assumptions!$B$27),0)</f>
+        <f>ROUND(B14*(1+Assumptions!$B$30),0)</f>
         <v>1254</v>
       </c>
       <c r="C15" s="12">
-        <f>MIN(B15,Assumptions!$B$33)</f>
+        <f>MIN(B15,Assumptions!$B$36)</f>
         <v>1254</v>
       </c>
       <c r="D15" s="11">
-        <f>C15*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$22</f>
-        <v>5327</v>
+        <f>C15*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$24</f>
+        <v>13127</v>
       </c>
       <c r="E15" s="11">
         <f>E14+D15</f>
-        <v>23831.5</v>
+        <v>109631.5</v>
       </c>
       <c r="F15" s="12">
-        <f>MIN(B15,Assumptions!$B$32)</f>
+        <f>MIN(B15,Assumptions!$B$35)</f>
         <v>1050</v>
       </c>
       <c r="G15" s="11">
-        <f>F15*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$22</f>
+        <f>F15*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$25</f>
         <v>2135</v>
       </c>
       <c r="H15" s="11">
@@ -2480,27 +2530,27 @@
         <v>12</v>
       </c>
       <c r="B16" s="28">
-        <f>ROUND(B15*(1+Assumptions!$B$27),0)</f>
+        <f>ROUND(B15*(1+Assumptions!$B$30),0)</f>
         <v>1329</v>
       </c>
       <c r="C16" s="28">
-        <f>MIN(B16,Assumptions!$B$33)</f>
+        <f>MIN(B16,Assumptions!$B$36)</f>
         <v>1329</v>
       </c>
       <c r="D16" s="29">
-        <f>C16*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$22</f>
-        <v>6114.5</v>
+        <f>C16*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$24</f>
+        <v>13914.5</v>
       </c>
       <c r="E16" s="29">
         <f>E15+D16</f>
-        <v>29946</v>
+        <v>123546</v>
       </c>
       <c r="F16" s="28">
-        <f>MIN(B16,Assumptions!$B$32)</f>
+        <f>MIN(B16,Assumptions!$B$35)</f>
         <v>1050</v>
       </c>
       <c r="G16" s="29">
-        <f>F16*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$22</f>
+        <f>F16*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$25</f>
         <v>2135</v>
       </c>
       <c r="H16" s="29">
@@ -2524,7 +2574,7 @@
       </c>
       <c r="D17" s="32">
         <f>SUM(D5:D16)</f>
-        <v>29946</v>
+        <v>123546</v>
       </c>
       <c r="E17" s="30" t="n"/>
       <c r="F17" s="31">
@@ -2545,7 +2595,7 @@
       </c>
       <c r="C19" s="33">
         <f>D17</f>
-        <v>29946</v>
+        <v>123546</v>
       </c>
     </row>
     <row r="20">
@@ -2567,7 +2617,7 @@
       </c>
       <c r="C21" s="34">
         <f>D17-G17</f>
-        <v>18319.5</v>
+        <v>111919.5</v>
       </c>
     </row>
   </sheetData>
@@ -2600,7 +2650,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Net profit at each volume (capped at labor capacity). Where a line crosses $0 is that method's break-even.</t>
+          <t>Net profit at each volume (capped at capacity). Where a line crosses $0 is that method's break-even.</t>
         </is>
       </c>
     </row>
@@ -2626,11 +2676,11 @@
         <v>0</v>
       </c>
       <c r="B5" s="11">
-        <f>MIN(A5,Assumptions!$B$33)*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$22</f>
-        <v>-7840</v>
+        <f>MIN(A5,Assumptions!$B$36)*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$24</f>
+        <v>-40</v>
       </c>
       <c r="C5" s="11">
-        <f>MIN(A5,Assumptions!$B$32)*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$22</f>
+        <f>MIN(A5,Assumptions!$B$35)*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$25</f>
         <v>-7840</v>
       </c>
     </row>
@@ -2639,11 +2689,11 @@
         <v>100</v>
       </c>
       <c r="B6" s="29">
-        <f>MIN(A6,Assumptions!$B$33)*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$22</f>
-        <v>-6790</v>
+        <f>MIN(A6,Assumptions!$B$36)*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$24</f>
+        <v>1010</v>
       </c>
       <c r="C6" s="29">
-        <f>MIN(A6,Assumptions!$B$32)*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$22</f>
+        <f>MIN(A6,Assumptions!$B$35)*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$25</f>
         <v>-6890</v>
       </c>
     </row>
@@ -2652,11 +2702,11 @@
         <v>200</v>
       </c>
       <c r="B7" s="11">
-        <f>MIN(A7,Assumptions!$B$33)*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$22</f>
-        <v>-5740</v>
+        <f>MIN(A7,Assumptions!$B$36)*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$24</f>
+        <v>2060</v>
       </c>
       <c r="C7" s="11">
-        <f>MIN(A7,Assumptions!$B$32)*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$22</f>
+        <f>MIN(A7,Assumptions!$B$35)*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$25</f>
         <v>-5940</v>
       </c>
     </row>
@@ -2665,11 +2715,11 @@
         <v>300</v>
       </c>
       <c r="B8" s="29">
-        <f>MIN(A8,Assumptions!$B$33)*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$22</f>
-        <v>-4690</v>
+        <f>MIN(A8,Assumptions!$B$36)*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$24</f>
+        <v>3110</v>
       </c>
       <c r="C8" s="29">
-        <f>MIN(A8,Assumptions!$B$32)*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$22</f>
+        <f>MIN(A8,Assumptions!$B$35)*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$25</f>
         <v>-4990</v>
       </c>
     </row>
@@ -2678,11 +2728,11 @@
         <v>400</v>
       </c>
       <c r="B9" s="11">
-        <f>MIN(A9,Assumptions!$B$33)*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$22</f>
-        <v>-3640</v>
+        <f>MIN(A9,Assumptions!$B$36)*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$24</f>
+        <v>4160</v>
       </c>
       <c r="C9" s="11">
-        <f>MIN(A9,Assumptions!$B$32)*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$22</f>
+        <f>MIN(A9,Assumptions!$B$35)*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$25</f>
         <v>-4040</v>
       </c>
     </row>
@@ -2691,11 +2741,11 @@
         <v>500</v>
       </c>
       <c r="B10" s="29">
-        <f>MIN(A10,Assumptions!$B$33)*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$22</f>
-        <v>-2590</v>
+        <f>MIN(A10,Assumptions!$B$36)*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$24</f>
+        <v>5210</v>
       </c>
       <c r="C10" s="29">
-        <f>MIN(A10,Assumptions!$B$32)*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$22</f>
+        <f>MIN(A10,Assumptions!$B$35)*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$25</f>
         <v>-3090</v>
       </c>
     </row>
@@ -2704,11 +2754,11 @@
         <v>600</v>
       </c>
       <c r="B11" s="11">
-        <f>MIN(A11,Assumptions!$B$33)*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$22</f>
-        <v>-1540</v>
+        <f>MIN(A11,Assumptions!$B$36)*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$24</f>
+        <v>6260</v>
       </c>
       <c r="C11" s="11">
-        <f>MIN(A11,Assumptions!$B$32)*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$22</f>
+        <f>MIN(A11,Assumptions!$B$35)*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$25</f>
         <v>-2140</v>
       </c>
     </row>
@@ -2717,11 +2767,11 @@
         <v>700</v>
       </c>
       <c r="B12" s="29">
-        <f>MIN(A12,Assumptions!$B$33)*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$22</f>
-        <v>-490</v>
+        <f>MIN(A12,Assumptions!$B$36)*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$24</f>
+        <v>7310</v>
       </c>
       <c r="C12" s="29">
-        <f>MIN(A12,Assumptions!$B$32)*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$22</f>
+        <f>MIN(A12,Assumptions!$B$35)*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$25</f>
         <v>-1190</v>
       </c>
     </row>
@@ -2730,11 +2780,11 @@
         <v>800</v>
       </c>
       <c r="B13" s="11">
-        <f>MIN(A13,Assumptions!$B$33)*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$22</f>
-        <v>560</v>
+        <f>MIN(A13,Assumptions!$B$36)*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$24</f>
+        <v>8360</v>
       </c>
       <c r="C13" s="11">
-        <f>MIN(A13,Assumptions!$B$32)*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$22</f>
+        <f>MIN(A13,Assumptions!$B$35)*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$25</f>
         <v>-240</v>
       </c>
     </row>
@@ -2743,11 +2793,11 @@
         <v>900</v>
       </c>
       <c r="B14" s="29">
-        <f>MIN(A14,Assumptions!$B$33)*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$22</f>
-        <v>1610</v>
+        <f>MIN(A14,Assumptions!$B$36)*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$24</f>
+        <v>9410</v>
       </c>
       <c r="C14" s="29">
-        <f>MIN(A14,Assumptions!$B$32)*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$22</f>
+        <f>MIN(A14,Assumptions!$B$35)*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$25</f>
         <v>710</v>
       </c>
     </row>
@@ -2756,11 +2806,11 @@
         <v>1000</v>
       </c>
       <c r="B15" s="11">
-        <f>MIN(A15,Assumptions!$B$33)*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$22</f>
-        <v>2660</v>
+        <f>MIN(A15,Assumptions!$B$36)*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$24</f>
+        <v>10460</v>
       </c>
       <c r="C15" s="11">
-        <f>MIN(A15,Assumptions!$B$32)*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$22</f>
+        <f>MIN(A15,Assumptions!$B$35)*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$25</f>
         <v>1660</v>
       </c>
     </row>
@@ -2769,11 +2819,11 @@
         <v>1100</v>
       </c>
       <c r="B16" s="29">
-        <f>MIN(A16,Assumptions!$B$33)*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$22</f>
-        <v>3710</v>
+        <f>MIN(A16,Assumptions!$B$36)*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$24</f>
+        <v>11510</v>
       </c>
       <c r="C16" s="29">
-        <f>MIN(A16,Assumptions!$B$32)*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$22</f>
+        <f>MIN(A16,Assumptions!$B$35)*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$25</f>
         <v>2135</v>
       </c>
     </row>
@@ -2782,11 +2832,11 @@
         <v>1200</v>
       </c>
       <c r="B17" s="11">
-        <f>MIN(A17,Assumptions!$B$33)*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$22</f>
-        <v>4760</v>
+        <f>MIN(A17,Assumptions!$B$36)*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$24</f>
+        <v>12560</v>
       </c>
       <c r="C17" s="11">
-        <f>MIN(A17,Assumptions!$B$32)*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$22</f>
+        <f>MIN(A17,Assumptions!$B$35)*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$25</f>
         <v>2135</v>
       </c>
     </row>
@@ -2795,11 +2845,11 @@
         <v>1300</v>
       </c>
       <c r="B18" s="29">
-        <f>MIN(A18,Assumptions!$B$33)*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$22</f>
-        <v>5810</v>
+        <f>MIN(A18,Assumptions!$B$36)*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$24</f>
+        <v>13610</v>
       </c>
       <c r="C18" s="29">
-        <f>MIN(A18,Assumptions!$B$32)*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$22</f>
+        <f>MIN(A18,Assumptions!$B$35)*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$25</f>
         <v>2135</v>
       </c>
     </row>
@@ -2808,11 +2858,11 @@
         <v>1400</v>
       </c>
       <c r="B19" s="11">
-        <f>MIN(A19,Assumptions!$B$33)*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$22</f>
-        <v>6860</v>
+        <f>MIN(A19,Assumptions!$B$36)*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$24</f>
+        <v>14660</v>
       </c>
       <c r="C19" s="11">
-        <f>MIN(A19,Assumptions!$B$32)*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$22</f>
+        <f>MIN(A19,Assumptions!$B$35)*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$25</f>
         <v>2135</v>
       </c>
     </row>
@@ -2821,11 +2871,11 @@
         <v>1500</v>
       </c>
       <c r="B20" s="29">
-        <f>MIN(A20,Assumptions!$B$33)*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$22</f>
-        <v>7910</v>
+        <f>MIN(A20,Assumptions!$B$36)*'Per-Unit'!$B$12-Assumptions!$B$13-Assumptions!$B$24</f>
+        <v>15710</v>
       </c>
       <c r="C20" s="29">
-        <f>MIN(A20,Assumptions!$B$32)*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$22</f>
+        <f>MIN(A20,Assumptions!$B$35)*'Per-Unit'!$C$12-Assumptions!$B$13-Assumptions!$B$25</f>
         <v>2135</v>
       </c>
     </row>
@@ -2836,11 +2886,11 @@
         </is>
       </c>
       <c r="B22" s="37">
-        <f>(Assumptions!$B$13+Assumptions!$B$22)/'Per-Unit'!$B$12</f>
-        <v>746.6666666666666</v>
+        <f>(Assumptions!$B$13+Assumptions!$B$24)/'Per-Unit'!$B$12</f>
+        <v>3.8095238095238093</v>
       </c>
       <c r="C22" s="37">
-        <f>(Assumptions!$B$13+Assumptions!$B$22)/'Per-Unit'!$C$12</f>
+        <f>(Assumptions!$B$13+Assumptions!$B$25)/'Per-Unit'!$C$12</f>
         <v>825.2631578947369</v>
       </c>
     </row>
@@ -2888,7 +2938,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Contribution, break-even and monthly net at the snapshot volume. Referral column is editable (blue).</t>
+          <t>Contribution, break-even and monthly net at snapshot volume. Referral is editable (blue). Labor per method from Assumptions.</t>
         </is>
       </c>
     </row>
@@ -2948,15 +2998,15 @@
         <v>11.600000000000001</v>
       </c>
       <c r="E5" s="41">
-        <f>(Assumptions!$B$13+Assumptions!$B$22)/D5</f>
+        <f>(Assumptions!$B$13+Assumptions!$B$25)/D5</f>
         <v>675.8620689655172</v>
       </c>
       <c r="F5" s="42">
-        <f>MIN(Assumptions!$B$25,Assumptions!$B$32)*D5-Assumptions!$B$13-Assumptions!$B$22</f>
+        <f>MIN(Assumptions!$B$28,Assumptions!$B$35)*D5-Assumptions!$B$13-Assumptions!$B$25</f>
         <v>2600.000000000002</v>
       </c>
       <c r="G5" s="43">
-        <f>F5/(MIN(Assumptions!$B$25,Assumptions!$B$32)*Assumptions!$B$5)</f>
+        <f>F5/(MIN(Assumptions!$B$28,Assumptions!$B$35)*Assumptions!$B$5)</f>
         <v>0.09629629629629637</v>
       </c>
     </row>
@@ -2979,16 +3029,16 @@
         <v>12.600000000000001</v>
       </c>
       <c r="E6" s="47">
-        <f>(Assumptions!$B$13+Assumptions!$B$22)/D6</f>
-        <v>622.2222222222222</v>
+        <f>(Assumptions!$B$13+Assumptions!$B$24)/D6</f>
+        <v>3.1746031746031744</v>
       </c>
       <c r="F6" s="48">
-        <f>MIN(Assumptions!$B$25,Assumptions!$B$33)*D6-Assumptions!$B$13-Assumptions!$B$22</f>
-        <v>3500.000000000002</v>
+        <f>MIN(Assumptions!$B$28,Assumptions!$B$36)*D6-Assumptions!$B$13-Assumptions!$B$24</f>
+        <v>11300.000000000002</v>
       </c>
       <c r="G6" s="49">
-        <f>F6/(MIN(Assumptions!$B$25,Assumptions!$B$33)*Assumptions!$B$5)</f>
-        <v>0.1296296296296297</v>
+        <f>F6/(MIN(Assumptions!$B$28,Assumptions!$B$36)*Assumptions!$B$5)</f>
+        <v>0.41851851851851857</v>
       </c>
     </row>
     <row r="7">
@@ -3010,15 +3060,15 @@
         <v>9.5</v>
       </c>
       <c r="E7" s="41">
-        <f>(Assumptions!$B$13+Assumptions!$B$22)/D7</f>
+        <f>(Assumptions!$B$13+Assumptions!$B$25)/D7</f>
         <v>825.2631578947369</v>
       </c>
       <c r="F7" s="42">
-        <f>MIN(Assumptions!$B$25,Assumptions!$B$32)*D7-Assumptions!$B$13-Assumptions!$B$22</f>
+        <f>MIN(Assumptions!$B$28,Assumptions!$B$35)*D7-Assumptions!$B$13-Assumptions!$B$25</f>
         <v>710</v>
       </c>
       <c r="G7" s="43">
-        <f>F7/(MIN(Assumptions!$B$25,Assumptions!$B$32)*Assumptions!$B$5)</f>
+        <f>F7/(MIN(Assumptions!$B$28,Assumptions!$B$35)*Assumptions!$B$5)</f>
         <v>0.026296296296296297</v>
       </c>
     </row>
@@ -3041,22 +3091,22 @@
         <v>10.5</v>
       </c>
       <c r="E8" s="47">
-        <f>(Assumptions!$B$13+Assumptions!$B$22)/D8</f>
-        <v>746.6666666666666</v>
+        <f>(Assumptions!$B$13+Assumptions!$B$24)/D8</f>
+        <v>3.8095238095238093</v>
       </c>
       <c r="F8" s="48">
-        <f>MIN(Assumptions!$B$25,Assumptions!$B$33)*D8-Assumptions!$B$13-Assumptions!$B$22</f>
-        <v>1610</v>
+        <f>MIN(Assumptions!$B$28,Assumptions!$B$36)*D8-Assumptions!$B$13-Assumptions!$B$24</f>
+        <v>9410</v>
       </c>
       <c r="G8" s="49">
-        <f>F8/(MIN(Assumptions!$B$25,Assumptions!$B$33)*Assumptions!$B$5)</f>
-        <v>0.05962962962962963</v>
+        <f>F8/(MIN(Assumptions!$B$28,Assumptions!$B$36)*Assumptions!$B$5)</f>
+        <v>0.3485185185185185</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Net @ snapshot uses Assumptions!B25 units, capped at each method's capacity.</t>
+          <t>Net @ snapshot uses Assumptions!B28 units, capped at each method's capacity.</t>
         </is>
       </c>
     </row>
